--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484190_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484190_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.9016</v>
+        <v>12.8097</v>
       </c>
       <c r="E2" t="n">
-        <v>12.8469</v>
+        <v>13.0736</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0547</v>
+        <v>-0.2639</v>
       </c>
       <c r="G2" t="n">
         <v>9.8254</v>
@@ -610,13 +610,13 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2746</v>
+        <v>0.1827</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8784</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>2.153</v>
+        <v>0.8344</v>
       </c>
       <c r="V2" t="n">
         <v>1.8097</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.9819</v>
+        <v>8.968999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>8.101599999999999</v>
+        <v>7.8182</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8803</v>
+        <v>1.1508</v>
       </c>
       <c r="G3" t="n">
         <v>4.6695</v>
@@ -688,13 +688,13 @@
         <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0383</v>
+        <v>0.0254</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2606</v>
+        <v>-0.544</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2989</v>
+        <v>0.5694</v>
       </c>
       <c r="V3" t="n">
         <v>3.2821</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4151</v>
+        <v>3.6329</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9709</v>
+        <v>2.5434</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4442</v>
+        <v>1.0895</v>
       </c>
       <c r="G4" t="n">
         <v>2.1117</v>
@@ -766,13 +766,13 @@
         <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7803</v>
+        <v>-0.5626</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2469</v>
+        <v>-0.6744</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5334</v>
+        <v>0.1118</v>
       </c>
       <c r="V4" t="n">
         <v>2.6789</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MARTIN VELA</t>
+          <t>J. ROSA DE SOUSA DA SILVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0973</v>
+        <v>0.2619</v>
       </c>
       <c r="E5" t="n">
-        <v>1.609</v>
+        <v>0.9933</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5117</v>
+        <v>-0.7313</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3198</v>
+        <v>0.9919</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0607</v>
+        <v>-0.9786</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2591</v>
+        <v>1.9705</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0081</v>
+        <v>1.9284</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0081</v>
+        <v>0.6706</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.2578</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3278</v>
+        <v>-0.9365</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0688</v>
+        <v>-1.6492</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2591</v>
+        <v>0.7127</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1984</v>
+        <v>1.9838</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.1984</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3968</v>
+        <v>2.1822</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4847</v>
+        <v>-0.9041</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7993</v>
+        <v>-0.7368</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3146</v>
+        <v>-0.1674</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.266</v>
+        <v>-1.8097</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="6">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2435</v>
+        <v>-0.1594</v>
       </c>
       <c r="E7" t="n">
         <v>-0.1045</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.139</v>
+        <v>-0.0548</v>
       </c>
       <c r="G7" t="n">
         <v>0.09710000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3407</v>
+        <v>-0.2565</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1247</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.216</v>
+        <v>-0.1318</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3621</v>
+        <v>-0.2156</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9913999999999999</v>
+        <v>1.0538</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3535</v>
+        <v>-1.2694</v>
       </c>
       <c r="G8" t="n">
         <v>1.0376</v>
@@ -1078,13 +1078,13 @@
         <v>0.3968</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.59</v>
+        <v>-0.4435</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3741</v>
+        <v>-0.3117</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.216</v>
+        <v>-0.1318</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2065</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MANYOSES ROCA</t>
+          <t>D. MARTIN VELA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7552</v>
+        <v>-0.4766</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1267</v>
+        <v>0.8948</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-1.3714</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3373</v>
+        <v>-0.3198</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.111</v>
+        <v>-0.0607</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4483</v>
+        <v>-0.2591</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0603</v>
+        <v>1.0081</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0202</v>
+        <v>1.0081</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.277</v>
+        <v>-1.3278</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1312</v>
+        <v>-1.0688</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4081</v>
+        <v>-0.2591</v>
       </c>
       <c r="P9" t="n">
         <v>0.1984</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4217</v>
+        <v>-0.0892</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.187</v>
+        <v>0.0851</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2347</v>
+        <v>-0.1743</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8692</v>
+        <v>-0.266</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8692</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. ROSA DE SOUSA DA SILVA</t>
+          <t>M. MANYOSES ROCA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9901</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3584</v>
+        <v>-0.1267</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3485</v>
+        <v>-0.5724</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9919</v>
+        <v>0.3373</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9786</v>
+        <v>-0.111</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9705</v>
+        <v>0.4483</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9284</v>
+        <v>0.0603</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6706</v>
+        <v>0.0202</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2578</v>
+        <v>0.0402</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9365</v>
+        <v>0.277</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6492</v>
+        <v>-0.1312</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7127</v>
+        <v>0.4081</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9838</v>
+        <v>0.1984</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1822</v>
+        <v>0.1984</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1562</v>
+        <v>-0.3656</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3716</v>
+        <v>-0.187</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7846</v>
+        <v>-0.1786</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8097</v>
+        <v>-0.8692</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8097</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="11">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6676</v>
+        <v>-5.122</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.8448</v>
+        <v>-6.7201</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1772</v>
+        <v>1.598</v>
       </c>
       <c r="G12" t="n">
         <v>-2.859</v>
@@ -1390,13 +1390,13 @@
         <v>2.3806</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2215</v>
+        <v>-0.676</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7537</v>
+        <v>-0.6291</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4677</v>
+        <v>-0.0469</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.9325</v>
+        <v>17.5559</v>
       </c>
       <c r="E13" t="n">
-        <v>17.5609</v>
+        <v>18.1845</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6283999999999998</v>
+        <v>-0.6285000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>15.4983</v>
@@ -1456,7 +1456,7 @@
         <v>-12.6061</v>
       </c>
       <c r="O13" t="n">
-        <v>6.2843</v>
+        <v>6.284300000000001</v>
       </c>
       <c r="P13" t="n">
         <v>1.9838</v>
@@ -1468,16 +1468,16 @@
         <v>11.9031</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.5064</v>
+        <v>-3.883</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.6471</v>
+        <v>-4.0237</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1407000000000003</v>
+        <v>0.1405999999999998</v>
       </c>
       <c r="V13" t="n">
-        <v>3.956599999999999</v>
+        <v>3.9566</v>
       </c>
       <c r="W13" t="n">
         <v>10.3071</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0303</v>
+        <v>2.6222</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9208</v>
+        <v>4.5127</v>
       </c>
       <c r="F14" t="n">
         <v>-1.8905</v>
@@ -1546,10 +1546,10 @@
         <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2357</v>
+        <v>0.8276</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5443</v>
+        <v>0.1362</v>
       </c>
       <c r="U14" t="n">
         <v>0.6914</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3277</v>
+        <v>0.4756</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6582</v>
+        <v>0.8622</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3305</v>
+        <v>-0.3866</v>
       </c>
       <c r="G15" t="n">
         <v>0.6453</v>
@@ -1624,13 +1624,13 @@
         <v>0.3968</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1111</v>
+        <v>0.0368</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2494</v>
+        <v>-0.0453</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1383</v>
+        <v>0.0822</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6032</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.257</v>
+        <v>0.4509</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1472</v>
+        <v>0.1589</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4042</v>
+        <v>0.292</v>
       </c>
       <c r="G16" t="n">
         <v>1.278</v>
@@ -1702,13 +1702,13 @@
         <v>0.3968</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1599</v>
+        <v>0.034</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7481</v>
+        <v>-0.4421</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5883</v>
+        <v>0.4761</v>
       </c>
       <c r="V16" t="n">
         <v>-0.266</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>U. LATORRE CIRIA</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8703</v>
+        <v>-1.0374</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7393</v>
+        <v>-1.1646</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.6096</v>
+        <v>0.1272</v>
       </c>
       <c r="G17" t="n">
-        <v>1.646</v>
+        <v>-2.9075</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1902</v>
+        <v>-1.0482</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5442</v>
+        <v>-1.8593</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6247</v>
+        <v>-1.1927</v>
       </c>
       <c r="K17" t="n">
-        <v>4.582</v>
+        <v>0.278</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0427</v>
+        <v>-1.4707</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9787</v>
+        <v>-1.7148</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3918</v>
+        <v>-1.3262</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.587</v>
+        <v>-0.3886</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2339</v>
+        <v>0.4138</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3005</v>
+        <v>-0.238</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9334</v>
+        <v>0.6518</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.3534</v>
+        <v>0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
-        <v>-4.1513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. TERREROS RIVAS</t>
+          <t>T. SARTOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9805</v>
+        <v>-1.1144</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2329</v>
+        <v>-0.216</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2135</v>
+        <v>-0.8984</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4011</v>
+        <v>-2.9454</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5049</v>
+        <v>-1.1938</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1039</v>
+        <v>-1.7516</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1207</v>
+        <v>-0.4468</v>
       </c>
       <c r="K18" t="n">
-        <v>3.836</v>
+        <v>-0.4118</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7153</v>
+        <v>-0.0351</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7197</v>
+        <v>-2.4985</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3311</v>
+        <v>-0.782</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3886</v>
+        <v>-1.7165</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5871</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3887</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>0.678</v>
+        <v>0.3585</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4252</v>
+        <v>-0.5157</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2527</v>
+        <v>0.8742</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4724</v>
+        <v>1.4724</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3373</v>
+        <v>1.7384</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1352</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>U. LATORRE CIRIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1292</v>
+        <v>-1.1789</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3687</v>
+        <v>3.7393</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2395</v>
+        <v>-4.9182</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9075</v>
+        <v>1.646</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0482</v>
+        <v>3.1902</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8593</v>
+        <v>-1.5442</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1927</v>
+        <v>4.6247</v>
       </c>
       <c r="K19" t="n">
-        <v>0.278</v>
+        <v>4.582</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4707</v>
+        <v>0.0427</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7148</v>
+        <v>-2.9787</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3262</v>
+        <v>-1.3918</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3886</v>
+        <v>-1.587</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1903</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>0.322</v>
+        <v>0.9253</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.442</v>
+        <v>0.3005</v>
       </c>
       <c r="U19" t="n">
-        <v>0.764</v>
+        <v>0.6248</v>
       </c>
       <c r="V19" t="n">
-        <v>0.266</v>
+        <v>-3.3534</v>
       </c>
       <c r="W19" t="n">
-        <v>0.266</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-4.1513</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. SARTOR</t>
+          <t>I. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0607</v>
+        <v>-1.4345</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1343</v>
+        <v>-0.2772</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9265</v>
+        <v>-1.1573</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9454</v>
+        <v>1.4011</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1938</v>
+        <v>2.5049</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7516</v>
+        <v>-1.1039</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4468</v>
+        <v>3.1207</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4118</v>
+        <v>3.836</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0351</v>
+        <v>-0.7153</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4985</v>
+        <v>-1.7197</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.782</v>
+        <v>-1.3311</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7165</v>
+        <v>-0.3886</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5878</v>
+        <v>0.2239</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4339</v>
+        <v>-0.0849</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8461</v>
+        <v>0.3089</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4724</v>
+        <v>-1.4724</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7384</v>
+        <v>-0.3373</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.266</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2539</v>
+        <v>-3.2641</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1544</v>
+        <v>-2.0524</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0995</v>
+        <v>-1.2117</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1082</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1122</v>
+        <v>0.102</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1247</v>
+        <v>-0.0227</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2369</v>
+        <v>0.1247</v>
       </c>
       <c r="V21" t="n">
         <v>-0.266</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>A. FERNANDEZ FUERTES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3202</v>
+        <v>-5.7517</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0434</v>
+        <v>-3.2586</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.2768</v>
+        <v>-2.4931</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.3284</v>
+        <v>-6.6836</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7284</v>
+        <v>-2.666</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.0567</v>
+        <v>-4.0176</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2759</v>
+        <v>-3.4458</v>
       </c>
       <c r="K22" t="n">
-        <v>3.125</v>
+        <v>-1.4103</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.401</v>
+        <v>-2.0355</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.0524</v>
+        <v>-3.2378</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3967</v>
+        <v>-1.2557</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.6558</v>
+        <v>-1.9821</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>2.413</v>
+        <v>0.5513</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2164</v>
+        <v>0.1872</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1966</v>
+        <v>0.3641</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.4129</v>
+        <v>-1.2065</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4129</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ FUERTES</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9326</v>
+        <v>-6.7001</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0748</v>
+        <v>-1.6758</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8578</v>
+        <v>-5.0243</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.6836</v>
+        <v>-4.3284</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.666</v>
+        <v>1.7284</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.0176</v>
+        <v>-6.0567</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.4458</v>
+        <v>-0.2759</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4103</v>
+        <v>3.125</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0355</v>
+        <v>-3.401</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.2378</v>
+        <v>-4.0524</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2557</v>
+        <v>-1.3967</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.9821</v>
+        <v>-2.6558</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5871</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6297</v>
+        <v>1.0331</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6291</v>
+        <v>0.5839</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4491</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2065</v>
+        <v>-2.4129</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2065</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="24">
@@ -2284,22 +2284,22 @@
         <v>-16.9324</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6283999999999992</v>
+        <v>0.6284999999999992</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.561</v>
+        <v>-17.5609</v>
       </c>
       <c r="G24" t="n">
         <v>-15.4983</v>
       </c>
       <c r="H24" t="n">
-        <v>2.671899999999999</v>
+        <v>2.6719</v>
       </c>
       <c r="I24" t="n">
         <v>-18.1703</v>
       </c>
       <c r="J24" t="n">
-        <v>6.321900000000001</v>
+        <v>6.321899999999999</v>
       </c>
       <c r="K24" t="n">
         <v>12.606</v>
@@ -2329,10 +2329,10 @@
         <v>4.5063</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1407999999999998</v>
+        <v>-0.1409</v>
       </c>
       <c r="U24" t="n">
-        <v>4.6471</v>
+        <v>4.6473</v>
       </c>
       <c r="V24" t="n">
         <v>-3.9566</v>
